--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/65.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/65.xlsx
@@ -426,13 +426,13 @@
         <v>-13.16388446308156</v>
       </c>
       <c r="E2">
-        <v>-6.76343650375355</v>
+        <v>-10.41479490935224</v>
       </c>
       <c r="F2">
-        <v>-0.6672923369400523</v>
+        <v>-1.378819345942091</v>
       </c>
       <c r="G2">
-        <v>-14.83913254135057</v>
+        <v>-17.20011761413814</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.54339729013563</v>
       </c>
       <c r="E3">
-        <v>-6.828900124008432</v>
+        <v>-10.17527486213854</v>
       </c>
       <c r="F3">
-        <v>-0.1922236314345358</v>
+        <v>-1.343200375989114</v>
       </c>
       <c r="G3">
-        <v>-14.33871544345264</v>
+        <v>-17.02576276749411</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.87029976980196</v>
       </c>
       <c r="E4">
-        <v>-7.053630175113081</v>
+        <v>-10.67559425592799</v>
       </c>
       <c r="F4">
-        <v>-0.541865915012568</v>
+        <v>-1.26699057493156</v>
       </c>
       <c r="G4">
-        <v>-13.92612380816604</v>
+        <v>-17.3270820013875</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.23932636432539</v>
       </c>
       <c r="E5">
-        <v>-7.775265150605391</v>
+        <v>-11.49285701704027</v>
       </c>
       <c r="F5">
-        <v>-0.2752566947889499</v>
+        <v>-0.9625050835823373</v>
       </c>
       <c r="G5">
-        <v>-13.71554662750408</v>
+        <v>-16.42115618038424</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.65023621525275</v>
       </c>
       <c r="E6">
-        <v>-8.925103571314994</v>
+        <v>-11.90476248430396</v>
       </c>
       <c r="F6">
-        <v>-0.1677718824387</v>
+        <v>-1.008858866708192</v>
       </c>
       <c r="G6">
-        <v>-13.11231060624747</v>
+        <v>-16.04243970232824</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.13609824167744</v>
       </c>
       <c r="E7">
-        <v>-10.13890668738294</v>
+        <v>-12.48428036001355</v>
       </c>
       <c r="F7">
-        <v>0.2573727764348959</v>
+        <v>-0.6562535129303461</v>
       </c>
       <c r="G7">
-        <v>-12.8212010947972</v>
+        <v>-14.7587342876566</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.704759520206784</v>
       </c>
       <c r="E8">
-        <v>-10.67391419207114</v>
+        <v>-13.55037371089931</v>
       </c>
       <c r="F8">
-        <v>0.5264430762122313</v>
+        <v>-0.8794546245124645</v>
       </c>
       <c r="G8">
-        <v>-11.79297213466388</v>
+        <v>-15.68006573232685</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.376645950731833</v>
       </c>
       <c r="E9">
-        <v>-12.03744224425469</v>
+        <v>-14.28603789886738</v>
       </c>
       <c r="F9">
-        <v>0.5954353120891936</v>
+        <v>-0.6134890457608216</v>
       </c>
       <c r="G9">
-        <v>-11.38933386978825</v>
+        <v>-14.46193725896985</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.157911166952982</v>
       </c>
       <c r="E10">
-        <v>-13.87716650918883</v>
+        <v>-14.61014531207035</v>
       </c>
       <c r="F10">
-        <v>0.06831365572656188</v>
+        <v>-0.6943385326414562</v>
       </c>
       <c r="G10">
-        <v>-11.02292931059279</v>
+        <v>-13.96955982091405</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.059519153466628</v>
       </c>
       <c r="E11">
-        <v>-12.90580430606953</v>
+        <v>-13.66796006698247</v>
       </c>
       <c r="F11">
-        <v>0.3826765999867658</v>
+        <v>-0.5472254521086808</v>
       </c>
       <c r="G11">
-        <v>-10.81886728355211</v>
+        <v>-13.73384235742686</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.083845940682016</v>
       </c>
       <c r="E12">
-        <v>-14.24804400194302</v>
+        <v>-15.56182223867831</v>
       </c>
       <c r="F12">
-        <v>0.4535202370089852</v>
+        <v>-0.4389338099081042</v>
       </c>
       <c r="G12">
-        <v>-9.945111688826728</v>
+        <v>-13.14595568056309</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.22992076603467</v>
       </c>
       <c r="E13">
-        <v>-14.90550144379863</v>
+        <v>-16.62236820890467</v>
       </c>
       <c r="F13">
-        <v>0.1094470674799741</v>
+        <v>-0.4227491675922074</v>
       </c>
       <c r="G13">
-        <v>-10.66985300773844</v>
+        <v>-12.39933496618233</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.490986641091276</v>
       </c>
       <c r="E14">
-        <v>-13.86514341069847</v>
+        <v>-17.02942820898015</v>
       </c>
       <c r="F14">
-        <v>0.6184854634394927</v>
+        <v>-0.1214139574758313</v>
       </c>
       <c r="G14">
-        <v>-9.047152695663733</v>
+        <v>-11.85913007672068</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.847959989790137</v>
       </c>
       <c r="E15">
-        <v>-17.35716745833728</v>
+        <v>-17.79321422053586</v>
       </c>
       <c r="F15">
-        <v>0.5039123112234875</v>
+        <v>0.5417604178573969</v>
       </c>
       <c r="G15">
-        <v>-8.413166672165605</v>
+        <v>-11.80626397500406</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.27504117559302</v>
       </c>
       <c r="E16">
-        <v>-16.50451467285505</v>
+        <v>-19.10806570561096</v>
       </c>
       <c r="F16">
-        <v>1.214084111154546</v>
+        <v>0.2016327622679199</v>
       </c>
       <c r="G16">
-        <v>-8.38688756167487</v>
+        <v>-11.61126291110437</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.73400267824345</v>
       </c>
       <c r="E17">
-        <v>-17.38606817945423</v>
+        <v>-19.57955683386757</v>
       </c>
       <c r="F17">
-        <v>1.091952934755398</v>
+        <v>0.4785385893083359</v>
       </c>
       <c r="G17">
-        <v>-8.079675556721583</v>
+        <v>-11.83930653003152</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.18746708561871</v>
       </c>
       <c r="E18">
-        <v>-18.71314654435004</v>
+        <v>-20.3094064612098</v>
       </c>
       <c r="F18">
-        <v>1.637641618084378</v>
+        <v>1.008554561376349</v>
       </c>
       <c r="G18">
-        <v>-7.394889211923338</v>
+        <v>-11.0438453373099</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.59072274584426</v>
       </c>
       <c r="E19">
-        <v>-19.28472600512419</v>
+        <v>-20.68646079251046</v>
       </c>
       <c r="F19">
-        <v>1.620166379354919</v>
+        <v>1.269735490009422</v>
       </c>
       <c r="G19">
-        <v>-7.258067675330799</v>
+        <v>-11.22036362546384</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.90988030287408</v>
       </c>
       <c r="E20">
-        <v>-19.9885323784483</v>
+        <v>-21.86773587978131</v>
       </c>
       <c r="F20">
-        <v>2.470346352604941</v>
+        <v>1.575386494294384</v>
       </c>
       <c r="G20">
-        <v>-7.355195770907476</v>
+        <v>-11.60990227688773</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.1116071243351</v>
       </c>
       <c r="E21">
-        <v>-20.76686837699065</v>
+        <v>-22.56823646707982</v>
       </c>
       <c r="F21">
-        <v>2.194770055246019</v>
+        <v>1.573345397013886</v>
       </c>
       <c r="G21">
-        <v>-7.309394373371659</v>
+        <v>-10.69001091952706</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.1826686336239</v>
       </c>
       <c r="E22">
-        <v>-20.63019903143916</v>
+        <v>-22.53043276606379</v>
       </c>
       <c r="F22">
-        <v>2.373240155444367</v>
+        <v>2.016598167312678</v>
       </c>
       <c r="G22">
-        <v>-7.304047842325736</v>
+        <v>-10.64505371110376</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.11524331403818</v>
       </c>
       <c r="E23">
-        <v>-21.85916800695879</v>
+        <v>-23.58202141470297</v>
       </c>
       <c r="F23">
-        <v>2.573416795065673</v>
+        <v>2.206925518514699</v>
       </c>
       <c r="G23">
-        <v>-7.190532546329666</v>
+        <v>-10.80348317843112</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.92507210573612</v>
       </c>
       <c r="E24">
-        <v>-21.54000115889819</v>
+        <v>-23.60128101465759</v>
       </c>
       <c r="F24">
-        <v>2.400443740952302</v>
+        <v>2.102923991093221</v>
       </c>
       <c r="G24">
-        <v>-6.474633694553351</v>
+        <v>-11.00115254203546</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.63237237724058</v>
       </c>
       <c r="E25">
-        <v>-22.3125905239248</v>
+        <v>-23.43824689343345</v>
       </c>
       <c r="F25">
-        <v>2.593658780920482</v>
+        <v>2.071906602062796</v>
       </c>
       <c r="G25">
-        <v>-6.951759449309732</v>
+        <v>-11.07303110678412</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.27588991877783</v>
       </c>
       <c r="E26">
-        <v>-22.36547857186039</v>
+        <v>-23.43755856538428</v>
       </c>
       <c r="F26">
-        <v>2.529334395358294</v>
+        <v>1.779757986443466</v>
       </c>
       <c r="G26">
-        <v>-7.317005317566443</v>
+        <v>-11.10830828005059</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.89079381374482</v>
       </c>
       <c r="E27">
-        <v>-22.9659723391735</v>
+        <v>-23.85434119915423</v>
       </c>
       <c r="F27">
-        <v>2.492420687154743</v>
+        <v>2.117052625515369</v>
       </c>
       <c r="G27">
-        <v>-7.635148743890404</v>
+        <v>-10.83457582213595</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.51963310657674</v>
       </c>
       <c r="E28">
-        <v>-23.06783130502803</v>
+        <v>-22.42635031947149</v>
       </c>
       <c r="F28">
-        <v>2.26682145194152</v>
+        <v>2.421504153801077</v>
       </c>
       <c r="G28">
-        <v>-6.802837868771157</v>
+        <v>-10.62750450920008</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.19374891245481</v>
       </c>
       <c r="E29">
-        <v>-22.13483886217573</v>
+        <v>-22.88577306449766</v>
       </c>
       <c r="F29">
-        <v>2.00241320390714</v>
+        <v>2.007030523810344</v>
       </c>
       <c r="G29">
-        <v>-6.38792057524322</v>
+        <v>-10.62616042771114</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.941302735401573</v>
       </c>
       <c r="E30">
-        <v>-22.02000128981521</v>
+        <v>-22.78329822617809</v>
       </c>
       <c r="F30">
-        <v>2.115047976400594</v>
+        <v>1.673972155636358</v>
       </c>
       <c r="G30">
-        <v>-7.285608103671995</v>
+        <v>-10.35309338944989</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.77599916503355</v>
       </c>
       <c r="E31">
-        <v>-21.12034294413337</v>
+        <v>-22.64810969162711</v>
       </c>
       <c r="F31">
-        <v>2.195008625058025</v>
+        <v>1.782919036452549</v>
       </c>
       <c r="G31">
-        <v>-6.133581293097633</v>
+        <v>-9.755331355242468</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.698856083336839</v>
       </c>
       <c r="E32">
-        <v>-20.8256434411362</v>
+        <v>-22.75081548212107</v>
       </c>
       <c r="F32">
-        <v>2.003104062321075</v>
+        <v>1.602402868769287</v>
       </c>
       <c r="G32">
-        <v>-6.029606989345742</v>
+        <v>-10.06869766435326</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.699634350297725</v>
       </c>
       <c r="E33">
-        <v>-20.08934526680706</v>
+        <v>-21.62534930852075</v>
       </c>
       <c r="F33">
-        <v>2.235065159187798</v>
+        <v>1.733101020848187</v>
       </c>
       <c r="G33">
-        <v>-5.966302737543799</v>
+        <v>-9.637989068603002</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.753785019007095</v>
       </c>
       <c r="E34">
-        <v>-20.55926954305702</v>
+        <v>-21.13818513172359</v>
       </c>
       <c r="F34">
-        <v>2.128020209928434</v>
+        <v>1.896334131039441</v>
       </c>
       <c r="G34">
-        <v>-5.475752720625673</v>
+        <v>-10.01073001196062</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.836768535236569</v>
       </c>
       <c r="E35">
-        <v>-18.86298469231584</v>
+        <v>-21.34910786557885</v>
       </c>
       <c r="F35">
-        <v>2.662529246789232</v>
+        <v>1.694050124745413</v>
       </c>
       <c r="G35">
-        <v>-6.880721763128051</v>
+        <v>-9.899565203297437</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.914117213514221</v>
       </c>
       <c r="E36">
-        <v>-18.45126489248647</v>
+        <v>-20.72680496744479</v>
       </c>
       <c r="F36">
-        <v>2.214745306797126</v>
+        <v>1.799893941270717</v>
       </c>
       <c r="G36">
-        <v>-5.683522558670333</v>
+        <v>-9.758545894961101</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.962008790566323</v>
       </c>
       <c r="E37">
-        <v>-19.64525140629685</v>
+        <v>-20.2778203550063</v>
       </c>
       <c r="F37">
-        <v>2.811116821298991</v>
+        <v>2.024560434788388</v>
       </c>
       <c r="G37">
-        <v>-5.927390585275206</v>
+        <v>-8.850678438999067</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.953082975993061</v>
       </c>
       <c r="E38">
-        <v>-17.73567090132039</v>
+        <v>-20.34555274073902</v>
       </c>
       <c r="F38">
-        <v>2.586478492273015</v>
+        <v>1.978219905540978</v>
       </c>
       <c r="G38">
-        <v>-7.341592739286611</v>
+        <v>-8.977922567346495</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.877163233023564</v>
       </c>
       <c r="E39">
-        <v>-18.25229733001145</v>
+        <v>-20.42189828403434</v>
       </c>
       <c r="F39">
-        <v>2.480127714897198</v>
+        <v>1.853437953452871</v>
       </c>
       <c r="G39">
-        <v>-6.369560289682423</v>
+        <v>-8.893377855364587</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.72368354446675</v>
       </c>
       <c r="E40">
-        <v>-18.80002078971319</v>
+        <v>-19.08499765901589</v>
       </c>
       <c r="F40">
-        <v>2.08574696462877</v>
+        <v>1.746412885011175</v>
       </c>
       <c r="G40">
-        <v>-5.733630975952742</v>
+        <v>-9.366818972935759</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.499603695569981</v>
       </c>
       <c r="E41">
-        <v>-17.30455564731616</v>
+        <v>-18.46377253769565</v>
       </c>
       <c r="F41">
-        <v>2.517094438614529</v>
+        <v>1.900812285218975</v>
       </c>
       <c r="G41">
-        <v>-5.816003970060887</v>
+        <v>-9.374737797865697</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.210202874090525</v>
       </c>
       <c r="E42">
-        <v>-16.97778549139668</v>
+        <v>-17.39587685415484</v>
       </c>
       <c r="F42">
-        <v>2.806446485882007</v>
+        <v>1.993576180454075</v>
       </c>
       <c r="G42">
-        <v>-5.777747305809069</v>
+        <v>-8.660623330135047</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.874953511316644</v>
       </c>
       <c r="E43">
-        <v>-16.96011991429275</v>
+        <v>-18.33342041338486</v>
       </c>
       <c r="F43">
-        <v>2.341260203491889</v>
+        <v>1.685334042933156</v>
       </c>
       <c r="G43">
-        <v>-6.217271884330408</v>
+        <v>-8.527221587084576</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.509300965679405</v>
       </c>
       <c r="E44">
-        <v>-14.98090959297436</v>
+        <v>-16.80584839027345</v>
       </c>
       <c r="F44">
-        <v>2.268252870813557</v>
+        <v>1.685595807032441</v>
       </c>
       <c r="G44">
-        <v>-6.831070201130061</v>
+        <v>-8.510907218667047</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.138098389929235</v>
       </c>
       <c r="E45">
-        <v>-13.3513518067362</v>
+        <v>-16.4129172291019</v>
       </c>
       <c r="F45">
-        <v>2.606089262166891</v>
+        <v>1.683316139939937</v>
       </c>
       <c r="G45">
-        <v>-7.321004456577883</v>
+        <v>-8.589605507226603</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.779322600355003</v>
       </c>
       <c r="E46">
-        <v>-14.29328798575366</v>
+        <v>-16.2882302257747</v>
       </c>
       <c r="F46">
-        <v>2.180064877111522</v>
+        <v>1.472718638391413</v>
       </c>
       <c r="G46">
-        <v>-6.776538895007187</v>
+        <v>-8.407184516376141</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.454100599312373</v>
       </c>
       <c r="E47">
-        <v>-13.03979279500848</v>
+        <v>-16.35106280263113</v>
       </c>
       <c r="F47">
-        <v>2.102120474712505</v>
+        <v>1.323243054025853</v>
       </c>
       <c r="G47">
-        <v>-5.149647432279765</v>
+        <v>-8.720607104761102</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.174495470308955</v>
       </c>
       <c r="E48">
-        <v>-14.14808699517172</v>
+        <v>-15.38657029458147</v>
       </c>
       <c r="F48">
-        <v>2.190782294568942</v>
+        <v>1.50501502669176</v>
       </c>
       <c r="G48">
-        <v>-5.487058233642284</v>
+        <v>-8.521603591304432</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.950403458042268</v>
       </c>
       <c r="E49">
-        <v>-12.8492889504538</v>
+        <v>-14.57229179784024</v>
       </c>
       <c r="F49">
-        <v>2.361599936700228</v>
+        <v>1.440761880726213</v>
       </c>
       <c r="G49">
-        <v>-7.265615719160337</v>
+        <v>-8.895023196497604</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.784087500248754</v>
       </c>
       <c r="E50">
-        <v>-11.99620143146684</v>
+        <v>-14.23737491718095</v>
       </c>
       <c r="F50">
-        <v>2.31274779748753</v>
+        <v>1.491565653539907</v>
       </c>
       <c r="G50">
-        <v>-6.450413743388043</v>
+        <v>-8.716021999189211</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.673521968991024</v>
       </c>
       <c r="E51">
-        <v>-11.58859801451044</v>
+        <v>-14.70085064644399</v>
       </c>
       <c r="F51">
-        <v>2.266756839284101</v>
+        <v>1.147203383787319</v>
       </c>
       <c r="G51">
-        <v>-7.745545505988481</v>
+        <v>-8.746432670512956</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.6137211802952</v>
       </c>
       <c r="E52">
-        <v>-11.54973465057661</v>
+        <v>-12.98577715704499</v>
       </c>
       <c r="F52">
-        <v>2.336246923970146</v>
+        <v>0.994263566943252</v>
       </c>
       <c r="G52">
-        <v>-6.476868312792359</v>
+        <v>-9.464930300537601</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.59537609141481</v>
       </c>
       <c r="E53">
-        <v>-10.13314193997118</v>
+        <v>-12.98778327103039</v>
       </c>
       <c r="F53">
-        <v>2.288736739949984</v>
+        <v>1.023072528477813</v>
       </c>
       <c r="G53">
-        <v>-6.859951400414664</v>
+        <v>-8.819522894928985</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.611172057096544</v>
       </c>
       <c r="E54">
-        <v>-9.939939124907928</v>
+        <v>-12.68912135327651</v>
       </c>
       <c r="F54">
-        <v>2.233984968094547</v>
+        <v>1.22034656871971</v>
       </c>
       <c r="G54">
-        <v>-7.076553773958099</v>
+        <v>-8.869978919493018</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.651701606382464</v>
       </c>
       <c r="E55">
-        <v>-11.05478149848626</v>
+        <v>-12.44290822147947</v>
       </c>
       <c r="F55">
-        <v>2.119181529740564</v>
+        <v>0.8925996923324744</v>
       </c>
       <c r="G55">
-        <v>-6.265860761210292</v>
+        <v>-9.398775669026344</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.712255554841811</v>
       </c>
       <c r="E56">
-        <v>-9.818517151340265</v>
+        <v>-11.92666671307906</v>
       </c>
       <c r="F56">
-        <v>2.469158473749327</v>
+        <v>0.7254053292210333</v>
       </c>
       <c r="G56">
-        <v>-6.828166852692121</v>
+        <v>-9.118759795678169</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.785747445353712</v>
       </c>
       <c r="E57">
-        <v>-9.82663217676201</v>
+        <v>-11.74279255447161</v>
       </c>
       <c r="F57">
-        <v>2.280078643855923</v>
+        <v>0.8125396395867077</v>
       </c>
       <c r="G57">
-        <v>-7.48332050436835</v>
+        <v>-9.271892390142698</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.870236103967573</v>
       </c>
       <c r="E58">
-        <v>-8.205587921658275</v>
+        <v>-12.04086577060449</v>
       </c>
       <c r="F58">
-        <v>2.347472959012885</v>
+        <v>0.9957562850030968</v>
       </c>
       <c r="G58">
-        <v>-7.042792830548611</v>
+        <v>-9.447976996830992</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.961042048025568</v>
       </c>
       <c r="E59">
-        <v>-8.840638474123926</v>
+        <v>-11.40896250757417</v>
       </c>
       <c r="F59">
-        <v>2.485223831159221</v>
+        <v>0.9191107626916697</v>
       </c>
       <c r="G59">
-        <v>-7.804870482052221</v>
+        <v>-9.677344833973857</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.059937430783654</v>
       </c>
       <c r="E60">
-        <v>-7.496578331699349</v>
+        <v>-11.07687592316968</v>
       </c>
       <c r="F60">
-        <v>1.878567306984197</v>
+        <v>0.964561625348473</v>
       </c>
       <c r="G60">
-        <v>-7.084095196696558</v>
+        <v>-10.07459043541316</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.163871613241309</v>
       </c>
       <c r="E61">
-        <v>-9.03435753522405</v>
+        <v>-11.27033233277736</v>
       </c>
       <c r="F61">
-        <v>1.977386567933761</v>
+        <v>1.060668811421272</v>
       </c>
       <c r="G61">
-        <v>-8.33978180919658</v>
+        <v>-10.10501103837353</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.275540115744029</v>
       </c>
       <c r="E62">
-        <v>-7.436693791421916</v>
+        <v>-10.93086433574036</v>
       </c>
       <c r="F62">
-        <v>2.437486674470691</v>
+        <v>1.19502669068574</v>
       </c>
       <c r="G62">
-        <v>-7.857918663773502</v>
+        <v>-10.46569828542266</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.389975881443186</v>
       </c>
       <c r="E63">
-        <v>-8.453041855333414</v>
+        <v>-10.96832387273181</v>
       </c>
       <c r="F63">
-        <v>1.910916710798323</v>
+        <v>1.124550848790364</v>
       </c>
       <c r="G63">
-        <v>-8.5397420703141</v>
+        <v>-9.639412603184889</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.50699989107524</v>
       </c>
       <c r="E64">
-        <v>-7.313510241465267</v>
+        <v>-10.87717474790542</v>
       </c>
       <c r="F64">
-        <v>2.324141162745634</v>
+        <v>1.193644973857871</v>
       </c>
       <c r="G64">
-        <v>-7.868211149855096</v>
+        <v>-11.20849200916002</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.618449422094399</v>
       </c>
       <c r="E65">
-        <v>-6.190656997367372</v>
+        <v>-10.45390281088248</v>
       </c>
       <c r="F65">
-        <v>2.033713894589322</v>
+        <v>0.9795848965656448</v>
       </c>
       <c r="G65">
-        <v>-8.876460967658911</v>
+        <v>-10.1934224675453</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.722184548241244</v>
       </c>
       <c r="E66">
-        <v>-7.663466184304025</v>
+        <v>-10.18838932286476</v>
       </c>
       <c r="F66">
-        <v>1.843777532801423</v>
+        <v>0.8677519837181004</v>
       </c>
       <c r="G66">
-        <v>-8.734316073839224</v>
+        <v>-10.23737658067021</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.809262552452391</v>
       </c>
       <c r="E67">
-        <v>-8.286597793181489</v>
+        <v>-10.82340817601235</v>
       </c>
       <c r="F67">
-        <v>2.40571878457333</v>
+        <v>1.026173936033895</v>
       </c>
       <c r="G67">
-        <v>-8.492040419638741</v>
+        <v>-10.83373163302344</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.877286850183188</v>
       </c>
       <c r="E68">
-        <v>-7.661306102202366</v>
+        <v>-10.99540867577169</v>
       </c>
       <c r="F68">
-        <v>2.055889289962265</v>
+        <v>1.010310700270284</v>
       </c>
       <c r="G68">
-        <v>-8.819489789473593</v>
+        <v>-10.97130466345339</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.91943865736886</v>
       </c>
       <c r="E69">
-        <v>-6.707351353168552</v>
+        <v>-10.78378402844524</v>
       </c>
       <c r="F69">
-        <v>2.196062308394386</v>
+        <v>0.7408245600567434</v>
       </c>
       <c r="G69">
-        <v>-8.601927357723769</v>
+        <v>-10.07156128624473</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.934931312036575</v>
       </c>
       <c r="E70">
-        <v>-7.687489738914716</v>
+        <v>-10.11995049518683</v>
       </c>
       <c r="F70">
-        <v>1.929593082261841</v>
+        <v>0.7434438577843954</v>
       </c>
       <c r="G70">
-        <v>-8.430527172973543</v>
+        <v>-10.44969510828582</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.920960182286059</v>
       </c>
       <c r="E71">
-        <v>-8.776216402890809</v>
+        <v>-8.410886290796009</v>
       </c>
       <c r="F71">
-        <v>1.93451358463447</v>
+        <v>1.014830272819958</v>
       </c>
       <c r="G71">
-        <v>-7.456998356785604</v>
+        <v>-10.3322468841891</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.878392693820538</v>
       </c>
       <c r="E72">
-        <v>-8.533838888578268</v>
+        <v>-10.87329837415486</v>
       </c>
       <c r="F72">
-        <v>2.305686793746067</v>
+        <v>1.029278657059587</v>
       </c>
       <c r="G72">
-        <v>-8.483711087061934</v>
+        <v>-10.89063991084351</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.808480492824874</v>
       </c>
       <c r="E73">
-        <v>-7.562377059030799</v>
+        <v>-10.92514487306868</v>
       </c>
       <c r="F73">
-        <v>1.755155474580321</v>
+        <v>0.7876322885193322</v>
       </c>
       <c r="G73">
-        <v>-7.581153746144891</v>
+        <v>-10.88365465975565</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.712347797580795</v>
       </c>
       <c r="E74">
-        <v>-9.322214513995624</v>
+        <v>-11.18785523567566</v>
       </c>
       <c r="F74">
-        <v>2.145922886237738</v>
+        <v>0.3130962232538158</v>
       </c>
       <c r="G74">
-        <v>-8.132392683888938</v>
+        <v>-10.13652081081631</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.594443914170813</v>
       </c>
       <c r="E75">
-        <v>-9.125986678295252</v>
+        <v>-11.49947764603949</v>
       </c>
       <c r="F75">
-        <v>1.664021806393931</v>
+        <v>0.4578782779151134</v>
       </c>
       <c r="G75">
-        <v>-8.395173857159666</v>
+        <v>-10.03049396883007</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.454691521494889</v>
       </c>
       <c r="E76">
-        <v>-8.295496244606561</v>
+        <v>-11.88918906219158</v>
       </c>
       <c r="F76">
-        <v>1.748843314970989</v>
+        <v>0.6896339396659422</v>
       </c>
       <c r="G76">
-        <v>-8.93116111160429</v>
+        <v>-10.36367058244786</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.297916807143548</v>
       </c>
       <c r="E77">
-        <v>-7.658398821889442</v>
+        <v>-10.95506450083736</v>
       </c>
       <c r="F77">
-        <v>1.489831052198445</v>
+        <v>0.4405919069534933</v>
       </c>
       <c r="G77">
-        <v>-7.652946236709527</v>
+        <v>-10.22129395044043</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.12227642217971</v>
       </c>
       <c r="E78">
-        <v>-8.796336412906888</v>
+        <v>-11.77863089776832</v>
       </c>
       <c r="F78">
-        <v>1.927558611920565</v>
+        <v>0.3936408709302201</v>
       </c>
       <c r="G78">
-        <v>-7.747243815850127</v>
+        <v>-10.07414020121982</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.932409750827082</v>
       </c>
       <c r="E79">
-        <v>-9.719275643462169</v>
+        <v>-12.66487590343944</v>
       </c>
       <c r="F79">
-        <v>1.483951300373374</v>
+        <v>0.4938029154397223</v>
       </c>
       <c r="G79">
-        <v>-8.037750808012252</v>
+        <v>-9.573751242958984</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.725738543160524</v>
       </c>
       <c r="E80">
-        <v>-11.05350446881609</v>
+        <v>-12.44551209403388</v>
       </c>
       <c r="F80">
-        <v>1.182693956792861</v>
+        <v>0.3890276928640297</v>
       </c>
       <c r="G80">
-        <v>-8.334719985067034</v>
+        <v>-10.31411502627051</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.506798538006284</v>
       </c>
       <c r="E81">
-        <v>-11.3664718359602</v>
+        <v>-13.35595273632799</v>
       </c>
       <c r="F81">
-        <v>1.311887793668278</v>
+        <v>0.630457857512154</v>
       </c>
       <c r="G81">
-        <v>-8.304451667201478</v>
+        <v>-9.766567346802756</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.272823288739637</v>
       </c>
       <c r="E82">
-        <v>-13.29601385436247</v>
+        <v>-13.37552480098915</v>
       </c>
       <c r="F82">
-        <v>1.425650802564345</v>
+        <v>0.02546552344935465</v>
       </c>
       <c r="G82">
-        <v>-7.062771972878113</v>
+        <v>-10.16636537885284</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.027858802772716</v>
       </c>
       <c r="E83">
-        <v>-13.77624493745389</v>
+        <v>-14.32870065249364</v>
       </c>
       <c r="F83">
-        <v>0.7841448617535463</v>
+        <v>0.1378584126611916</v>
       </c>
       <c r="G83">
-        <v>-5.917164310104397</v>
+        <v>-9.818516427404999</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.771129287072486</v>
       </c>
       <c r="E84">
-        <v>-12.80651298497735</v>
+        <v>-16.12373340744608</v>
       </c>
       <c r="F84">
-        <v>0.9714287911176809</v>
+        <v>0.3958965153680432</v>
       </c>
       <c r="G84">
-        <v>-6.745767374219661</v>
+        <v>-9.741417132340912</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.509222129153319</v>
       </c>
       <c r="E85">
-        <v>-15.23492981396062</v>
+        <v>-16.7012632830663</v>
       </c>
       <c r="F85">
-        <v>0.8480749444320009</v>
+        <v>-0.4738519810383118</v>
       </c>
       <c r="G85">
-        <v>-6.392767213912713</v>
+        <v>-9.364342684872385</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.246180081251543</v>
       </c>
       <c r="E86">
-        <v>-15.08965636779455</v>
+        <v>-17.53862341182463</v>
       </c>
       <c r="F86">
-        <v>0.8678298502539635</v>
+        <v>0.06261697309750967</v>
       </c>
       <c r="G86">
-        <v>-7.138182889717171</v>
+        <v>-9.240892441712962</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.992795076086953</v>
       </c>
       <c r="E87">
-        <v>-16.08361112773812</v>
+        <v>-19.22351462196251</v>
       </c>
       <c r="F87">
-        <v>0.4545639799365125</v>
+        <v>-0.1988398018806955</v>
       </c>
       <c r="G87">
-        <v>-6.902160856040371</v>
+        <v>-9.462447391383147</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.758036872490626</v>
       </c>
       <c r="E88">
-        <v>-17.48069517231851</v>
+        <v>-19.84395178880541</v>
       </c>
       <c r="F88">
-        <v>0.5297399784753732</v>
+        <v>-0.02196099546312544</v>
       </c>
       <c r="G88">
-        <v>-6.400894603211624</v>
+        <v>-9.832476997944106</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.556163086294978</v>
       </c>
       <c r="E89">
-        <v>-19.48027909819742</v>
+        <v>-20.78150893345745</v>
       </c>
       <c r="F89">
-        <v>0.3708657375576505</v>
+        <v>-0.2411188457521795</v>
       </c>
       <c r="G89">
-        <v>-6.817890919338223</v>
+        <v>-9.405817199388373</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.399086584783783</v>
       </c>
       <c r="E90">
-        <v>-20.09540436502932</v>
+        <v>-22.63580129927426</v>
       </c>
       <c r="F90">
-        <v>0.3478404372294355</v>
+        <v>-0.3409263490132835</v>
       </c>
       <c r="G90">
-        <v>-6.649043165198774</v>
+        <v>-9.302177260735951</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.302412203895238</v>
       </c>
       <c r="E91">
-        <v>-23.32723135313541</v>
+        <v>-24.58292738224831</v>
       </c>
       <c r="F91">
-        <v>0.3517022860612867</v>
+        <v>-0.1992813217063876</v>
       </c>
       <c r="G91">
-        <v>-6.387089628312864</v>
+        <v>-9.525377551539153</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.276941934224066</v>
       </c>
       <c r="E92">
-        <v>-26.38055495280715</v>
+        <v>-26.84422993492652</v>
       </c>
       <c r="F92">
-        <v>0.1993373561947625</v>
+        <v>-0.8223403488242441</v>
       </c>
       <c r="G92">
-        <v>-6.320368893514392</v>
+        <v>-9.041336067151233</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.335907049432412</v>
       </c>
       <c r="E93">
-        <v>-25.90755584270598</v>
+        <v>-28.51065855653513</v>
       </c>
       <c r="F93">
-        <v>0.02828777119069257</v>
+        <v>-0.9772872998852945</v>
       </c>
       <c r="G93">
-        <v>-6.063523528395576</v>
+        <v>-9.163425676094016</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.485626492445055</v>
       </c>
       <c r="E94">
-        <v>-28.81012201418836</v>
+        <v>-30.57897339666545</v>
       </c>
       <c r="F94">
-        <v>-0.3303787468734374</v>
+        <v>-0.4154860422044614</v>
       </c>
       <c r="G94">
-        <v>-6.799815340693803</v>
+        <v>-9.23159311929315</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.730486736740464</v>
       </c>
       <c r="E95">
-        <v>-30.3294431576578</v>
+        <v>-33.17409920353009</v>
       </c>
       <c r="F95">
-        <v>0.1925182357349169</v>
+        <v>-0.6992532364422657</v>
       </c>
       <c r="G95">
-        <v>-7.788678603819645</v>
+        <v>-9.400364730885194</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.074214728717148</v>
       </c>
       <c r="E96">
-        <v>-33.08354557303571</v>
+        <v>-34.05547609964297</v>
       </c>
       <c r="F96">
-        <v>-0.08323036204378807</v>
+        <v>-0.6826519253227608</v>
       </c>
       <c r="G96">
-        <v>-6.535223299013092</v>
+        <v>-9.541956763599822</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.5033621957297</v>
       </c>
       <c r="E97">
-        <v>-36.24274263076978</v>
+        <v>-37.35949149190534</v>
       </c>
       <c r="F97">
-        <v>-0.5048296084334021</v>
+        <v>-1.196046705453602</v>
       </c>
       <c r="G97">
-        <v>-6.69158036483287</v>
+        <v>-9.746015480094959</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.024534116270212</v>
       </c>
       <c r="E98">
-        <v>-37.92542394559192</v>
+        <v>-39.25696512162229</v>
       </c>
       <c r="F98">
-        <v>-0.4817819421853114</v>
+        <v>-1.097506604318781</v>
       </c>
       <c r="G98">
-        <v>-6.141592813302669</v>
+        <v>-9.724496934089697</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.598792395280629</v>
       </c>
       <c r="E99">
-        <v>-41.96844101116601</v>
+        <v>-42.10839802884706</v>
       </c>
       <c r="F99">
-        <v>-1.129370584834867</v>
+        <v>-1.077729332576943</v>
       </c>
       <c r="G99">
-        <v>-6.890156817914974</v>
+        <v>-9.810819409026193</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.25082825419781</v>
       </c>
       <c r="E100">
-        <v>-42.9539094108192</v>
+        <v>-44.81060639633408</v>
       </c>
       <c r="F100">
-        <v>-1.209776066787601</v>
+        <v>-1.305197364650882</v>
       </c>
       <c r="G100">
-        <v>-6.755023659547463</v>
+        <v>-9.345465954207461</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.896485255392602</v>
       </c>
       <c r="E101">
-        <v>-46.61648484653489</v>
+        <v>-46.33527113913257</v>
       </c>
       <c r="F101">
-        <v>-1.337719897252193</v>
+        <v>-1.211514809966077</v>
       </c>
       <c r="G101">
-        <v>-8.002781515480931</v>
+        <v>-9.298002662810928</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.625763153652256</v>
       </c>
       <c r="E102">
-        <v>-48.47381242205535</v>
+        <v>-49.66178399026504</v>
       </c>
       <c r="F102">
-        <v>-0.9136719968199036</v>
+        <v>-1.506356448011908</v>
       </c>
       <c r="G102">
-        <v>-6.912049455566174</v>
+        <v>-9.722321905670396</v>
       </c>
     </row>
   </sheetData>
